--- a/data/output/evaluasi_36.xlsx
+++ b/data/output/evaluasi_36.xlsx
@@ -8,8 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="3600" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="3603" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3672" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="3673" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3674" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="3601" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="3602" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="3603" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="3671" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="3604" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,20 +479,412 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-3.439979228967389</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25 vs q-to-q_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>q2-25</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>0.92497790264333</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="D3" t="n">
+        <v>4.668518544214451</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q2-25 vs q-to-q_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3.5353416200406</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q3-25 vs y-on-y_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.280719498427749</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q1-25 vs y-on-y_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>36</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.1297640623530656</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25 vs y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.280719498427749</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q1-25 vs c-to-c_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>36</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.435581538306781</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q2-25 vs implisit_q-to-q_pkrt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>36</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.9249784606975545</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>implisit_q-to-q_pklnprt_q2-25 vs implisit_q-to-q_pklnprt_q2-25.1</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>36</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.134690800136449</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25 vs implisit_q-to-q_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>36</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.6534476377638342</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q1-25 vs implisit_q-to-q_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>36</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1.617658290385481</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q2-25 vs implisit_q-to-q_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>36</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5.32273380152427</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q2-25 vs implisit_y-on-y_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>36</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>4.251219137712813</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25 vs implisit_y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>36</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4.720652966455944</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q1-25 vs implisit_y-on-y_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>36</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>5.125213119393184</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q2-25 vs implisit_y-on-y_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -501,7 +899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,85 +936,253 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3603</v>
+        <v>3672</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Tangerang</t>
+          <t>Kota Cilegon</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>124623.7840096627</v>
+        <v>2.035215679400685</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3603</v>
+        <v>3672</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Tangerang</t>
+          <t>Kota Cilegon</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>65847.7252430471</v>
+        <v>-0.6946177190957767</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3603</v>
+        <v>3672</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Tangerang</t>
+          <t>Kota Cilegon</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.3766479747337625</v>
+        <v>1.275254527769983</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3672</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Cilegon</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-6.989782307381713</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3672</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Cilegon</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-17.72853277793509</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3672</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Cilegon</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3641907015982486</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3672</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Cilegon</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-9.038703666278373</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3672</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Cilegon</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1027846931044042</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3672</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Cilegon</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.984632276242112</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -631,7 +1197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -677,20 +1243,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-32153.1938290786</v>
+        <v>2.348916186700869</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -705,20 +1271,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-7037.68189608131</v>
+        <v>2.26965038379538</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -733,20 +1299,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.3181995126701362</v>
+        <v>-0.3838444827404393</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>q-to-q_pmtb_q1-25_ril vs q-to-q_pmtb_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -761,20 +1327,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.301659648275062</v>
+        <v>-1.14935512969407</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>y-on-y_pmtb_q1-25_ril vs y-on-y_pmtb_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -789,20 +1355,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.301659648275062</v>
+        <v>-0.5718715821618789</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>c-to-c_pmtb_q1-25_ril vs c-to-c_pmtb_q1-25_rev</t>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -817,20 +1383,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.344543139543233</v>
+        <v>0.115339629969021</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -845,20 +1411,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.9229546406942936</v>
+        <v>0.06586113756730091</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -873,20 +1439,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.04648521516662686</v>
+        <v>-1.616829264029924</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -901,104 +1467,772 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.09460031127384622</v>
+        <v>-2.889172608835033</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
+          <t>sog_q_pi_q3-25</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>3673</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Kota Serang</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>2.908671252760234</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>implisit_y-on-y_pkrt_q1-25_ril vs implisit_y-on-y_pkrt_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>3673</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Kota Serang</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>-0.1139174327923194</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>sog_q_pmtb_q1-25_ril vs sog_q_pmtb_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>3673</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Kota Serang</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0.8314171884496186</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pmtb_q1-25_ril vs sog_y-on-y_pmtb_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3674</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Tangerang Selatan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.828715909292548</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3674</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Tangerang Selatan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.44754840272175</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3601</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Pandeglang</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1.516726868846526</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3601</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Pandeglang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-2.808369606842884</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3601</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Pandeglang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>8.88286146689796</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3601</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Pandeglang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-2.13153406676211</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3601</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Pandeglang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5289222780569359</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3602</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Lebak</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.439429007896423</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3602</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Lebak</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3995668530105353</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3603</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Tangerang</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1.494593390482541</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3603</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Tangerang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5.981753445412238</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3603</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Tangerang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5079283513217713</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3603</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Tangerang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4.343149869035964</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3671</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Tangerang</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5289933450095072</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3671</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Tangerang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.4099449492818038</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3604</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Serang</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4.765844914959038</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3604</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Serang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-4.500105525880066</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_36.xlsx
+++ b/data/output/evaluasi_36.xlsx
@@ -492,7 +492,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
